--- a/backend/public/templates/student_bulk_template.xlsx
+++ b/backend/public/templates/student_bulk_template.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+  <si>
+    <t>Admission Date</t>
+  </si>
   <si>
     <t>First Name</t>
   </si>
@@ -25,13 +28,25 @@
     <t>Gender</t>
   </si>
   <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Assigned Teacher</t>
+  </si>
+  <si>
+    <t>Academic Year</t>
+  </si>
+  <si>
     <t>Blood Group</t>
   </si>
   <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>Email</t>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>Email Address</t>
   </si>
   <si>
     <t>Address</t>
@@ -46,67 +61,73 @@
     <t>Pincode</t>
   </si>
   <si>
-    <t>Admission Date</t>
-  </si>
-  <si>
-    <t>Class</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>Father Name</t>
-  </si>
-  <si>
-    <t>Father Phone</t>
-  </si>
-  <si>
-    <t>Father WhatsApp</t>
-  </si>
-  <si>
-    <t>Father Email</t>
-  </si>
-  <si>
-    <t>Father Occupation</t>
-  </si>
-  <si>
-    <t>Mother Name</t>
-  </si>
-  <si>
-    <t>Mother Phone</t>
-  </si>
-  <si>
-    <t>Mother WhatsApp</t>
-  </si>
-  <si>
-    <t>Mother Email</t>
-  </si>
-  <si>
-    <t>Mother Occupation</t>
-  </si>
-  <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t>2009-02-14</t>
+    <t>Father's Name</t>
+  </si>
+  <si>
+    <t>Father's Phone</t>
+  </si>
+  <si>
+    <t>Father's WhatsApp</t>
+  </si>
+  <si>
+    <t>Father's Email</t>
+  </si>
+  <si>
+    <t>Father's Occupation</t>
+  </si>
+  <si>
+    <t>Mother's Name</t>
+  </si>
+  <si>
+    <t>Mother's Phone</t>
+  </si>
+  <si>
+    <t>Mother's WhatsApp</t>
+  </si>
+  <si>
+    <t>Mother's Email</t>
+  </si>
+  <si>
+    <t>Mother's Occupation</t>
+  </si>
+  <si>
+    <t>2025-06-10</t>
+  </si>
+  <si>
+    <t>Aarav</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>2010-04-15</t>
   </si>
   <si>
     <t>Male</t>
   </si>
   <si>
+    <t>Class 6</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Rajesh Teacher</t>
+  </si>
+  <si>
+    <t>2025-26</t>
+  </si>
+  <si>
     <t>A+</t>
   </si>
   <si>
     <t>9876543210</t>
   </si>
   <si>
-    <t>alex.johnson@email.com</t>
-  </si>
-  <si>
-    <t>123 Main Street</t>
+    <t>aarav.sharma@student.com</t>
+  </si>
+  <si>
+    <t>12 MG Road</t>
   </si>
   <si>
     <t>Mumbai</t>
@@ -118,157 +139,28 @@
     <t>400001</t>
   </si>
   <si>
-    <t>2024-06-01</t>
-  </si>
-  <si>
-    <t>Class 6</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Robert Johnson</t>
+    <t>Rajesh Sharma</t>
   </si>
   <si>
     <t>9876543211</t>
   </si>
   <si>
-    <t>robert.j@email.com</t>
-  </si>
-  <si>
-    <t>Engineer</t>
-  </si>
-  <si>
-    <t>Mary Johnson</t>
+    <t>rajesh.sharma@gmail.com</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Sunita Sharma</t>
   </si>
   <si>
     <t>9876543212</t>
   </si>
   <si>
-    <t>mary.j@email.com</t>
-  </si>
-  <si>
-    <t>Teacher</t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>Wilson</t>
-  </si>
-  <si>
-    <t>2010-11-05</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>O-</t>
-  </si>
-  <si>
-    <t>8765432109</t>
-  </si>
-  <si>
-    <t>emma.wilson@email.com</t>
-  </si>
-  <si>
-    <t>456 Park Avenue</t>
-  </si>
-  <si>
-    <t>Delhi</t>
-  </si>
-  <si>
-    <t>110001</t>
-  </si>
-  <si>
-    <t>Class 7</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>David Wilson</t>
-  </si>
-  <si>
-    <t>8765432110</t>
-  </si>
-  <si>
-    <t>david.w@email.com</t>
+    <t>sunita.sharma@gmail.com</t>
   </si>
   <si>
     <t>Doctor</t>
-  </si>
-  <si>
-    <t>Sarah Wilson</t>
-  </si>
-  <si>
-    <t>8765432111</t>
-  </si>
-  <si>
-    <t>sarah.w@email.com</t>
-  </si>
-  <si>
-    <t>Nurse</t>
-  </si>
-  <si>
-    <t>Daniel</t>
-  </si>
-  <si>
-    <t>Brown</t>
-  </si>
-  <si>
-    <t>2009-07-22</t>
-  </si>
-  <si>
-    <t>B+</t>
-  </si>
-  <si>
-    <t>7654321098</t>
-  </si>
-  <si>
-    <t>daniel.brown@email.com</t>
-  </si>
-  <si>
-    <t>789 Lake Road</t>
-  </si>
-  <si>
-    <t>Bangalore</t>
-  </si>
-  <si>
-    <t>Karnataka</t>
-  </si>
-  <si>
-    <t>560001</t>
-  </si>
-  <si>
-    <t>Class 8</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Michael Brown</t>
-  </si>
-  <si>
-    <t>7654321099</t>
-  </si>
-  <si>
-    <t>michael.b@email.com</t>
-  </si>
-  <si>
-    <t>Business</t>
-  </si>
-  <si>
-    <t>Lisa Brown</t>
-  </si>
-  <si>
-    <t>7654321100</t>
-  </si>
-  <si>
-    <t>lisa.b@email.com</t>
-  </si>
-  <si>
-    <t>Accountant</t>
   </si>
 </sst>
 </file>
@@ -655,29 +547,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
-    <col min="9" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="20" customWidth="1"/>
-    <col min="16" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="25" customWidth="1"/>
-    <col min="19" max="20" width="20" customWidth="1"/>
-    <col min="21" max="22" width="15" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="20" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="13" width="30" customWidth="1"/>
+    <col min="14" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="25" customWidth="1"/>
+    <col min="21" max="22" width="20" customWidth="1"/>
+    <col min="23" max="24" width="15" customWidth="1"/>
+    <col min="25" max="25" width="25" customWidth="1"/>
+    <col min="26" max="26" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,227 +644,91 @@
       <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="W2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="X2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" t="s">
+      <c r="Y2" t="s">
         <v>48</v>
       </c>
-      <c r="D3" t="s">
+      <c r="Z2" t="s">
         <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
-        <v>54</v>
-      </c>
-      <c r="J3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K3" t="s">
-        <v>55</v>
-      </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" t="s">
-        <v>56</v>
-      </c>
-      <c r="N3" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>59</v>
-      </c>
-      <c r="R3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S3" t="s">
-        <v>61</v>
-      </c>
-      <c r="T3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U3" t="s">
-        <v>63</v>
-      </c>
-      <c r="V3" t="s">
-        <v>63</v>
-      </c>
-      <c r="W3" t="s">
-        <v>64</v>
-      </c>
-      <c r="X3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>69</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H4" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K4" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N4" t="s">
-        <v>77</v>
-      </c>
-      <c r="O4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P4" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>79</v>
-      </c>
-      <c r="R4" t="s">
-        <v>80</v>
-      </c>
-      <c r="S4" t="s">
-        <v>81</v>
-      </c>
-      <c r="T4" t="s">
-        <v>82</v>
-      </c>
-      <c r="U4" t="s">
-        <v>83</v>
-      </c>
-      <c r="V4" t="s">
-        <v>83</v>
-      </c>
-      <c r="W4" t="s">
-        <v>84</v>
-      </c>
-      <c r="X4" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>
